--- a/changes/template.xlsx
+++ b/changes/template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-dev\deadline-balancing\changes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B326E017-4350-41AE-99A3-BD75EB1C1CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141877E7-4395-4DE8-9560-A8085A45EED8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>new</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>buck_barrel_deviation</t>
+  </si>
+  <si>
+    <t>muzzle_loudness</t>
   </si>
 </sst>
 </file>
@@ -926,19 +929,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="27.140625" customWidth="1"/>
-    <col min="3" max="22" width="6.7109375" customWidth="1"/>
+    <col min="3" max="23" width="6.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="C1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -978,11 +981,14 @@
       <c r="M2" t="s">
         <v>12</v>
       </c>
-      <c r="N2" t="s">
+      <c r="N2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="O2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
@@ -996,12 +1002,13 @@
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
-      <c r="N3">
-        <f>C3-D3*20-E3*0.8-F3*0.6-H3*5+I3*10+J3/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N3" s="1"/>
+      <c r="O3">
+        <f>C3-D3*20-E3*0.8-F3*0.6-H3*10+I3*15+J3/200-M3*5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
@@ -1015,12 +1022,13 @@
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
-      <c r="N4">
-        <f t="shared" ref="N4:N36" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*5+I4*10+J4/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N4" s="1"/>
+      <c r="O4">
+        <f t="shared" ref="O4:O39" si="0">C4-D4*20-E4*0.8-F4*0.6-H4*10+I4*15+J4/200-M4*5</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
@@ -1034,12 +1042,13 @@
       <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
-      <c r="N5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N5" s="1"/>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
@@ -1053,12 +1062,13 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
-      <c r="N6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N6" s="1"/>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
@@ -1072,12 +1082,13 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
-      <c r="N7">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N7" s="1"/>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -1091,12 +1102,13 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
-      <c r="N8">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N8" s="1"/>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
@@ -1110,12 +1122,13 @@
       <c r="K9" s="1"/>
       <c r="L9" s="1"/>
       <c r="M9" s="1"/>
-      <c r="N9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N9" s="1"/>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
@@ -1129,12 +1142,13 @@
       <c r="K10" s="1"/>
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
-      <c r="N10">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N10" s="1"/>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
@@ -1148,12 +1162,13 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="1"/>
-      <c r="N11">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N11" s="1"/>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
@@ -1167,12 +1182,13 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
-      <c r="N12">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N12" s="1"/>
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
@@ -1186,12 +1202,13 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
-      <c r="N13">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N13" s="1"/>
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
@@ -1205,12 +1222,13 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="1"/>
-      <c r="N14">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N14" s="1"/>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1224,12 +1242,13 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
-      <c r="N15">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N15" s="1"/>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
@@ -1243,12 +1262,13 @@
       <c r="K16" s="1"/>
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
-      <c r="N16">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N16" s="1"/>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
@@ -1262,12 +1282,13 @@
       <c r="K17" s="1"/>
       <c r="L17" s="1"/>
       <c r="M17" s="1"/>
-      <c r="N17">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N17" s="1"/>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1281,12 +1302,13 @@
       <c r="K18" s="1"/>
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
-      <c r="N18">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N18" s="1"/>
+      <c r="O18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
@@ -1300,12 +1322,13 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="1"/>
-      <c r="N19">
-        <f>C19-D19*20-E19*0.8-F19*0.6-H19*5+I19*10+J19/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N19" s="1"/>
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
@@ -1319,12 +1342,13 @@
       <c r="K20" s="1"/>
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
-      <c r="N20">
-        <f>C20-D20*20-E20*0.8-F20*0.6-H20*5+I20*10+J20/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N20" s="1"/>
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1338,12 +1362,13 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
-      <c r="N21">
-        <f>C21-D21*20-E21*0.8-F21*0.6-H21*5+I21*10+J21/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N21" s="1"/>
+      <c r="O21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1357,12 +1382,13 @@
       <c r="K22" s="1"/>
       <c r="L22" s="1"/>
       <c r="M22" s="1"/>
-      <c r="N22">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N22" s="1"/>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1376,12 +1402,13 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
-      <c r="N23">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N23" s="1"/>
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1395,12 +1422,13 @@
       <c r="K24" s="1"/>
       <c r="L24" s="1"/>
       <c r="M24" s="1"/>
-      <c r="N24">
-        <f>C24-D24*20-E24*0.8-F24*0.6-H24*5+I24*10+J24/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N24" s="1"/>
+      <c r="O24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -1414,12 +1442,13 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25">
-        <f>C25-D25*20-E25*0.8-F25*0.6-H25*5+I25*10+J25/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N25" s="1"/>
+      <c r="O25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
@@ -1433,12 +1462,13 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="1"/>
-      <c r="N26">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N26" s="1"/>
+      <c r="O26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
@@ -1452,12 +1482,13 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="1"/>
-      <c r="N27">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N27" s="1"/>
+      <c r="O27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
@@ -1471,12 +1502,13 @@
       <c r="K28" s="1"/>
       <c r="L28" s="1"/>
       <c r="M28" s="1"/>
-      <c r="N28">
-        <f>C28-D28*20-E28*0.8-F28*0.6-H28*5+I28*10+J28/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N28" s="1"/>
+      <c r="O28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
@@ -1490,12 +1522,13 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="1"/>
-      <c r="N29">
-        <f>C29-D29*20-E29*0.8-F29*0.6-H29*5+I29*10+J29/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N29" s="1"/>
+      <c r="O29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
@@ -1509,12 +1542,13 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="1"/>
-      <c r="N30">
-        <f t="shared" ref="N30:N31" si="1">C30-D30*20-E30*0.8-F30*0.6-H30*5+I30*10+J30/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N30" s="1"/>
+      <c r="O30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
@@ -1528,12 +1562,13 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
-      <c r="N31">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N31" s="1"/>
+      <c r="O31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
@@ -1547,12 +1582,13 @@
       <c r="K32" s="1"/>
       <c r="L32" s="1"/>
       <c r="M32" s="1"/>
-      <c r="N32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N32" s="1"/>
+      <c r="O32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
@@ -1566,12 +1602,13 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="1"/>
-      <c r="N33">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N33" s="1"/>
+      <c r="O33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -1585,12 +1622,13 @@
       <c r="K34" s="1"/>
       <c r="L34" s="1"/>
       <c r="M34" s="1"/>
-      <c r="N34">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N34" s="1"/>
+      <c r="O34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="C35" s="1"/>
@@ -1604,12 +1642,13 @@
       <c r="K35" s="1"/>
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
-      <c r="N35">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N35" s="1"/>
+      <c r="O35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="C36" s="1"/>
@@ -1623,12 +1662,13 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
-      <c r="N36">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N36" s="1"/>
+      <c r="O36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="C37" s="1"/>
@@ -1642,12 +1682,13 @@
       <c r="K37" s="1"/>
       <c r="L37" s="1"/>
       <c r="M37" s="1"/>
-      <c r="N37">
-        <f>C37-D37*20-E37*0.8-F37*0.6-H37*5+I37*10+J37/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N37" s="1"/>
+      <c r="O37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="C38" s="1"/>
@@ -1661,12 +1702,13 @@
       <c r="K38" s="1"/>
       <c r="L38" s="1"/>
       <c r="M38" s="1"/>
-      <c r="N38">
-        <f>C38-D38*20-E38*0.8-F38*0.6-H38*5+I38*10+J38/300</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="N38" s="1"/>
+      <c r="O38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
@@ -1680,8 +1722,9 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
-      <c r="N39">
-        <f>C39-D39*20-E39*0.8-F39*0.6-H39*5+I39*10+J39/300</f>
+      <c r="N39" s="1"/>
+      <c r="O39">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
